--- a/tests/fixtures/sample.xlsx
+++ b/tests/fixtures/sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,13 +455,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.575</v>
+        <v>2.292</v>
       </c>
       <c r="D2" t="n">
-        <v>648.9</v>
+        <v>657.505</v>
       </c>
       <c r="E2" t="n">
-        <v>1.852</v>
+        <v>1.894</v>
       </c>
     </row>
     <row r="3">
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.728</v>
+        <v>2.11</v>
       </c>
       <c r="D3" t="n">
-        <v>648.1</v>
+        <v>636.978</v>
       </c>
       <c r="E3" t="n">
-        <v>1.781</v>
+        <v>1.813</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.737</v>
+        <v>2.437</v>
       </c>
       <c r="D4" t="n">
-        <v>656.1</v>
+        <v>649.832</v>
       </c>
       <c r="E4" t="n">
-        <v>1.762</v>
+        <v>1.715</v>
       </c>
     </row>
     <row r="5">
@@ -518,13 +518,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.581</v>
+        <v>2.676</v>
       </c>
       <c r="D5" t="n">
-        <v>646.3</v>
+        <v>657.778</v>
       </c>
       <c r="E5" t="n">
-        <v>1.763</v>
+        <v>1.807</v>
       </c>
     </row>
     <row r="6">
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.536</v>
+        <v>2.725</v>
       </c>
       <c r="D6" t="n">
-        <v>634.7</v>
+        <v>654.675</v>
       </c>
       <c r="E6" t="n">
-        <v>1.662</v>
+        <v>1.714</v>
       </c>
     </row>
     <row r="7">
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.416</v>
+        <v>2.574</v>
       </c>
       <c r="D7" t="n">
-        <v>641.9</v>
+        <v>640.4109999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.825</v>
+        <v>1.888</v>
       </c>
     </row>
     <row r="8">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.364</v>
+        <v>2.49</v>
       </c>
       <c r="D8" t="n">
-        <v>638.7</v>
+        <v>648.151</v>
       </c>
       <c r="E8" t="n">
-        <v>1.917</v>
+        <v>1.732</v>
       </c>
     </row>
     <row r="9">
@@ -602,124 +602,124 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.466</v>
+        <v>2.745</v>
       </c>
       <c r="D9" t="n">
-        <v>650.5</v>
+        <v>648.455</v>
       </c>
       <c r="E9" t="n">
-        <v>1.686</v>
+        <v>1.757</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B组-01</t>
+          <t>A组-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B组</t>
+          <t>A组</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.491</v>
+        <v>2.43</v>
       </c>
       <c r="D10" t="n">
-        <v>646.1</v>
+        <v>655.323</v>
       </c>
       <c r="E10" t="n">
-        <v>1.785</v>
+        <v>1.837</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B组-02</t>
+          <t>A组-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B组</t>
+          <t>A组</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.675</v>
+        <v>2.583</v>
       </c>
       <c r="D11" t="n">
-        <v>639</v>
+        <v>654.308</v>
       </c>
       <c r="E11" t="n">
-        <v>1.871</v>
+        <v>2.014</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B组-03</t>
+          <t>A组-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B组</t>
+          <t>A组</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.48</v>
+        <v>2.419</v>
       </c>
       <c r="D12" t="n">
-        <v>663.5</v>
+        <v>644.878</v>
       </c>
       <c r="E12" t="n">
-        <v>1.899</v>
+        <v>1.719</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B组-04</t>
+          <t>A组-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B组</t>
+          <t>A组</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.388</v>
+        <v>2.623</v>
       </c>
       <c r="D13" t="n">
-        <v>653.2</v>
+        <v>661.29</v>
       </c>
       <c r="E13" t="n">
-        <v>1.778</v>
+        <v>1.789</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B组-05</t>
+          <t>A组-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B组</t>
+          <t>A组</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.642</v>
+        <v>2.332</v>
       </c>
       <c r="D14" t="n">
-        <v>625.4</v>
+        <v>641.755</v>
       </c>
       <c r="E14" t="n">
-        <v>1.767</v>
+        <v>1.865</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B组-06</t>
+          <t>B组-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -728,19 +728,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.639</v>
+        <v>2.609</v>
       </c>
       <c r="D15" t="n">
-        <v>652.4</v>
+        <v>643.345</v>
       </c>
       <c r="E15" t="n">
-        <v>1.917</v>
+        <v>1.823</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B组-07</t>
+          <t>B组-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.577</v>
+        <v>2.523</v>
       </c>
       <c r="D16" t="n">
-        <v>642</v>
+        <v>652.187</v>
       </c>
       <c r="E16" t="n">
-        <v>1.752</v>
+        <v>1.887</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B组-08</t>
+          <t>B组-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.456</v>
+        <v>2.545</v>
       </c>
       <c r="D17" t="n">
-        <v>640.4</v>
+        <v>656.789</v>
       </c>
       <c r="E17" t="n">
-        <v>2.006</v>
+        <v>1.807</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B组-09</t>
+          <t>B组-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.669</v>
+        <v>2.558</v>
       </c>
       <c r="D18" t="n">
-        <v>627.4</v>
+        <v>656.313</v>
       </c>
       <c r="E18" t="n">
-        <v>1.932</v>
+        <v>1.654</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B组-10</t>
+          <t>B组-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -812,139 +812,412 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.523</v>
+        <v>2.436</v>
       </c>
       <c r="D19" t="n">
-        <v>638.2</v>
+        <v>645.296</v>
       </c>
       <c r="E19" t="n">
-        <v>1.961</v>
+        <v>1.736</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C组-01</t>
+          <t>B组-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C组</t>
+          <t>B组</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.524</v>
+        <v>2.445</v>
       </c>
       <c r="D20" t="n">
-        <v>660.6</v>
+        <v>664.949</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7</v>
+        <v>1.713</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C组-02</t>
+          <t>B组-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C组</t>
+          <t>B组</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.363</v>
+        <v>2.694</v>
       </c>
       <c r="D21" t="n">
-        <v>657</v>
+        <v>633.171</v>
       </c>
       <c r="E21" t="n">
-        <v>1.809</v>
+        <v>1.767</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C组-03</t>
+          <t>B组-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C组</t>
+          <t>B组</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.342</v>
+        <v>2.533</v>
       </c>
       <c r="D22" t="n">
-        <v>653.9</v>
+        <v>655.862</v>
       </c>
       <c r="E22" t="n">
-        <v>1.684</v>
+        <v>1.871</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C组-04</t>
+          <t>B组-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C组</t>
+          <t>B组</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.256</v>
+        <v>2.659</v>
       </c>
       <c r="D23" t="n">
-        <v>659.9</v>
+        <v>646.513</v>
       </c>
       <c r="E23" t="n">
-        <v>1.831</v>
+        <v>1.754</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C组-05</t>
+          <t>B组-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>C组</t>
+          <t>B组</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.391</v>
+        <v>2.672</v>
       </c>
       <c r="D24" t="n">
-        <v>661</v>
+        <v>648.087</v>
       </c>
       <c r="E24" t="n">
-        <v>1.772</v>
+        <v>1.672</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>B组-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>B组</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2.273</v>
+      </c>
+      <c r="D25" t="n">
+        <v>640.8049999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B组-12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>B组</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2.528</v>
+      </c>
+      <c r="D26" t="n">
+        <v>656.905</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.757</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B组-13</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>B组</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="D27" t="n">
+        <v>656.256</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.769</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B组-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B组</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2.591</v>
+      </c>
+      <c r="D28" t="n">
+        <v>643.381</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.764</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B组-15</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B组</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2.424</v>
+      </c>
+      <c r="D29" t="n">
+        <v>638.042</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.849</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C组-01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C组</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2.406</v>
+      </c>
+      <c r="D30" t="n">
+        <v>650.125</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.848</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C组-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C组</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2.589</v>
+      </c>
+      <c r="D31" t="n">
+        <v>656.654</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C组-03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>C组</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="D32" t="n">
+        <v>649.203</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.631</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C组-04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C组</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2.211</v>
+      </c>
+      <c r="D33" t="n">
+        <v>636.773</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C组-05</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>C组</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="D34" t="n">
+        <v>640.9450000000001</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.762</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>C组-06</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>C组</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="D25" t="n">
-        <v>657.2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1.842</v>
+      <c r="C35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D35" t="n">
+        <v>646.437</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.874</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C组-07</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C组</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2.313</v>
+      </c>
+      <c r="D36" t="n">
+        <v>647.946</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.705</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C组-08</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C组</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="D37" t="n">
+        <v>658.403</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.627</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C组-09</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>C组</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2.587</v>
+      </c>
+      <c r="D38" t="n">
+        <v>652.377</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.741</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/sample.xlsx
+++ b/tests/fixtures/sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
